--- a/templates/csv/○○_用語.xlsx
+++ b/templates/csv/○○_用語.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Owner\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F1FC066-536A-4065-89EF-CF8FA3A688D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF108384-EB19-4ED9-8822-16C3F8D102AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="744" windowWidth="11904" windowHeight="10584" xr2:uid="{06E41477-E298-4D6D-BEA8-DB6E391F9FBC}"/>
+    <workbookView xWindow="336" yWindow="1164" windowWidth="11904" windowHeight="10584" xr2:uid="{06E41477-E298-4D6D-BEA8-DB6E391F9FBC}"/>
   </bookViews>
   <sheets>
     <sheet name="○○_用語" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>id</t>
   </si>
   <si>
     <t>ジャンル</t>
-  </si>
-  <si>
-    <t>満点</t>
   </si>
   <si>
     <t>問題文</t>
@@ -1021,10 +1018,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B92BED4F-7209-4083-B768-63A97F5660A2}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1040,19 +1037,16 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2">
-        <v>5</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -1060,51 +1054,48 @@
       <c r="E2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11">
         <v>10</v>
       </c>
